--- a/artfynd/A 25111-2023 artfynd.xlsx
+++ b/artfynd/A 25111-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924328</v>
+        <v>122924329</v>
       </c>
       <c r="B2" t="n">
         <v>107999</v>

--- a/artfynd/A 25111-2023 artfynd.xlsx
+++ b/artfynd/A 25111-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924329</v>
+        <v>122924328</v>
       </c>
       <c r="B2" t="n">
-        <v>107999</v>
+        <v>108007</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25111-2023 artfynd.xlsx
+++ b/artfynd/A 25111-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924328</v>
+        <v>122924329</v>
       </c>
       <c r="B2" t="n">
         <v>108007</v>

--- a/artfynd/A 25111-2023 artfynd.xlsx
+++ b/artfynd/A 25111-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122924329</v>
       </c>
       <c r="B2" t="n">
-        <v>108007</v>
+        <v>108011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25111-2023 artfynd.xlsx
+++ b/artfynd/A 25111-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122924329</v>
       </c>
       <c r="B2" t="n">
-        <v>108011</v>
+        <v>108013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25111-2023 artfynd.xlsx
+++ b/artfynd/A 25111-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122924329</v>
       </c>
       <c r="B2" t="n">
-        <v>108013</v>
+        <v>108019</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25111-2023 artfynd.xlsx
+++ b/artfynd/A 25111-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122924329</v>
+        <v>122924328</v>
       </c>
       <c r="B2" t="n">
-        <v>108019</v>
+        <v>108022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25111-2023 artfynd.xlsx
+++ b/artfynd/A 25111-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122924328</v>
       </c>
       <c r="B2" t="n">
-        <v>108022</v>
+        <v>108039</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 25111-2023 artfynd.xlsx
+++ b/artfynd/A 25111-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122924328</v>
       </c>
       <c r="B2" t="n">
-        <v>108039</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
